--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488290_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488290_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>7.2836</v>
+        <v>7.1245</v>
       </c>
       <c r="E2" t="n">
-        <v>7.0825</v>
+        <v>6.8002</v>
       </c>
       <c r="F2" t="n">
-        <v>0.2011</v>
+        <v>0.3242</v>
       </c>
       <c r="G2" t="n">
         <v>2.637</v>
@@ -610,13 +610,13 @@
         <v>2.2234</v>
       </c>
       <c r="S2" t="n">
-        <v>0.8319</v>
+        <v>0.6728</v>
       </c>
       <c r="T2" t="n">
-        <v>1.1926</v>
+        <v>0.9103</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.3606</v>
+        <v>-0.2375</v>
       </c>
       <c r="V2" t="n">
         <v>2.5177</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>M. GEDEAO YIMBU</t>
+          <t>J. MIAVIVULULU NZIKULU</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>6.714</v>
+        <v>4.5717</v>
       </c>
       <c r="E3" t="n">
-        <v>4.5123</v>
+        <v>3.5126</v>
       </c>
       <c r="F3" t="n">
-        <v>2.2017</v>
+        <v>1.059</v>
       </c>
       <c r="G3" t="n">
-        <v>-1.2851</v>
+        <v>5.8303</v>
       </c>
       <c r="H3" t="n">
-        <v>-2.0579</v>
+        <v>3.6368</v>
       </c>
       <c r="I3" t="n">
-        <v>0.7728</v>
+        <v>2.1935</v>
       </c>
       <c r="J3" t="n">
-        <v>-0.8446</v>
+        <v>5.3334</v>
       </c>
       <c r="K3" t="n">
-        <v>-1.0105</v>
+        <v>3.9849</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1659</v>
+        <v>1.3484</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.4405</v>
+        <v>0.4969</v>
       </c>
       <c r="N3" t="n">
-        <v>-1.0474</v>
+        <v>-0.3481</v>
       </c>
       <c r="O3" t="n">
-        <v>0.6069</v>
+        <v>0.845</v>
       </c>
       <c r="P3" t="n">
-        <v>1.1117</v>
+        <v>-1.8529</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.9264</v>
+        <v>-3.7057</v>
       </c>
       <c r="R3" t="n">
-        <v>2.0382</v>
+        <v>1.8529</v>
       </c>
       <c r="S3" t="n">
-        <v>4.4961</v>
+        <v>0.0901</v>
       </c>
       <c r="T3" t="n">
-        <v>2.8229</v>
+        <v>0.6261</v>
       </c>
       <c r="U3" t="n">
-        <v>1.6733</v>
+        <v>-0.536</v>
       </c>
       <c r="V3" t="n">
-        <v>2.3913</v>
+        <v>0.5041</v>
       </c>
       <c r="W3" t="n">
-        <v>3.4605</v>
+        <v>1.2589</v>
       </c>
       <c r="X3" t="n">
-        <v>-1.0692</v>
+        <v>-0.7548</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>J. MIAVIVULULU NZIKULU</t>
+          <t>M. GEDEAO YIMBU</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>4.2664</v>
+        <v>3.9971</v>
       </c>
       <c r="E4" t="n">
-        <v>3.2074</v>
+        <v>2.7064</v>
       </c>
       <c r="F4" t="n">
-        <v>1.059</v>
+        <v>1.2907</v>
       </c>
       <c r="G4" t="n">
-        <v>5.8303</v>
+        <v>-1.2851</v>
       </c>
       <c r="H4" t="n">
-        <v>3.6368</v>
+        <v>-2.0579</v>
       </c>
       <c r="I4" t="n">
-        <v>2.1935</v>
+        <v>0.7728</v>
       </c>
       <c r="J4" t="n">
-        <v>5.3334</v>
+        <v>-0.8446</v>
       </c>
       <c r="K4" t="n">
-        <v>3.9849</v>
+        <v>-1.0105</v>
       </c>
       <c r="L4" t="n">
-        <v>1.3484</v>
+        <v>0.1659</v>
       </c>
       <c r="M4" t="n">
-        <v>0.4969</v>
+        <v>-0.4405</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.3481</v>
+        <v>-1.0474</v>
       </c>
       <c r="O4" t="n">
-        <v>0.845</v>
+        <v>0.6069</v>
       </c>
       <c r="P4" t="n">
-        <v>-1.8529</v>
+        <v>1.1117</v>
       </c>
       <c r="Q4" t="n">
-        <v>-3.7057</v>
+        <v>-0.9264</v>
       </c>
       <c r="R4" t="n">
-        <v>1.8529</v>
+        <v>2.0382</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.2151</v>
+        <v>1.7792</v>
       </c>
       <c r="T4" t="n">
-        <v>0.3209</v>
+        <v>1.0169</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.536</v>
+        <v>0.7623</v>
       </c>
       <c r="V4" t="n">
-        <v>0.5041</v>
+        <v>2.3913</v>
       </c>
       <c r="W4" t="n">
-        <v>1.2589</v>
+        <v>3.4605</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.7548</v>
+        <v>-1.0692</v>
       </c>
     </row>
     <row r="5">
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.2659</v>
+        <v>3.2326</v>
       </c>
       <c r="E5" t="n">
-        <v>-1.5982</v>
+        <v>-0.7054</v>
       </c>
       <c r="F5" t="n">
-        <v>3.8641</v>
+        <v>3.938</v>
       </c>
       <c r="G5" t="n">
         <v>0.1237</v>
@@ -844,13 +844,13 @@
         <v>2.7793</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.8436</v>
+        <v>0.1231</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.6056</v>
+        <v>0.2873</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.238</v>
+        <v>-0.1642</v>
       </c>
       <c r="V5" t="n">
         <v>1.133</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.6897</v>
+        <v>0.7143</v>
       </c>
       <c r="E7" t="n">
         <v>0.9877</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.298</v>
+        <v>-0.2734</v>
       </c>
       <c r="G7" t="n">
         <v>0.9877</v>
@@ -1000,13 +1000,13 @@
         <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>0.0164</v>
+        <v>0.041</v>
       </c>
       <c r="T7" t="n">
         <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0164</v>
+        <v>0.041</v>
       </c>
       <c r="V7" t="n">
         <v>-0.3144</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.6718</v>
+        <v>0.4021</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.3401</v>
+        <v>-0.5359</v>
       </c>
       <c r="F8" t="n">
-        <v>1.0119</v>
+        <v>0.9379999999999999</v>
       </c>
       <c r="G8" t="n">
         <v>0.08939999999999999</v>
@@ -1078,13 +1078,13 @@
         <v>0.7411</v>
       </c>
       <c r="S8" t="n">
-        <v>0.7678</v>
+        <v>0.498</v>
       </c>
       <c r="T8" t="n">
-        <v>0.5434</v>
+        <v>0.3476</v>
       </c>
       <c r="U8" t="n">
-        <v>0.2243</v>
+        <v>0.1505</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.7066</v>
+        <v>-0.5594</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.7408</v>
+        <v>-0.6429</v>
       </c>
       <c r="F9" t="n">
-        <v>0.0342</v>
+        <v>0.0835</v>
       </c>
       <c r="G9" t="n">
         <v>-0.5008</v>
@@ -1156,13 +1156,13 @@
         <v>0.1853</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.0766</v>
+        <v>0.0706</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.1094</v>
+        <v>-0.0115</v>
       </c>
       <c r="U9" t="n">
-        <v>0.0328</v>
+        <v>0.08210000000000001</v>
       </c>
       <c r="V9" t="n">
         <v>-0.3144</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>F. GARRIDO SOTO</t>
+          <t>R. CARRETERO GONZALEZ</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.0676</v>
+        <v>-0.9792</v>
       </c>
       <c r="E10" t="n">
-        <v>0.9167</v>
+        <v>1.5528</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.9843</v>
+        <v>-2.532</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.5467</v>
+        <v>2.4342</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.553</v>
+        <v>0.889</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.9937</v>
+        <v>1.5451</v>
       </c>
       <c r="J10" t="n">
-        <v>0.0626</v>
+        <v>3.1818</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.1033</v>
+        <v>1.2836</v>
       </c>
       <c r="L10" t="n">
-        <v>0.1659</v>
+        <v>1.8982</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.6093</v>
+        <v>-0.7477</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.4497</v>
+        <v>-0.3945</v>
       </c>
       <c r="O10" t="n">
-        <v>-1.1596</v>
+        <v>-0.3531</v>
       </c>
       <c r="P10" t="n">
-        <v>1.6676</v>
+        <v>-0.5558999999999999</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>-1.8529</v>
       </c>
       <c r="R10" t="n">
-        <v>1.6676</v>
+        <v>1.297</v>
       </c>
       <c r="S10" t="n">
-        <v>0.0704</v>
+        <v>-0.2139</v>
       </c>
       <c r="T10" t="n">
-        <v>0.5397</v>
+        <v>0.2239</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.4693</v>
+        <v>-0.4377</v>
       </c>
       <c r="V10" t="n">
-        <v>-1.2589</v>
+        <v>-2.6436</v>
       </c>
       <c r="W10" t="n">
-        <v>0.3144</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.5733</v>
+        <v>-2.6436</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>R. CARRETERO GONZALEZ</t>
+          <t>F. GARRIDO SOTO</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.8497</v>
+        <v>-1.2213</v>
       </c>
       <c r="E11" t="n">
-        <v>1.0517</v>
+        <v>0.6891</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.9013</v>
+        <v>-1.9104</v>
       </c>
       <c r="G11" t="n">
-        <v>2.4342</v>
+        <v>-1.5467</v>
       </c>
       <c r="H11" t="n">
-        <v>0.889</v>
+        <v>-0.553</v>
       </c>
       <c r="I11" t="n">
-        <v>1.5451</v>
+        <v>-0.9937</v>
       </c>
       <c r="J11" t="n">
-        <v>3.1818</v>
+        <v>0.0626</v>
       </c>
       <c r="K11" t="n">
-        <v>1.2836</v>
+        <v>-0.1033</v>
       </c>
       <c r="L11" t="n">
-        <v>1.8982</v>
+        <v>0.1659</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.7477</v>
+        <v>-1.6093</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.3945</v>
+        <v>-0.4497</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.3531</v>
+        <v>-1.1596</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.5558999999999999</v>
+        <v>1.6676</v>
       </c>
       <c r="Q11" t="n">
-        <v>-1.8529</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>1.297</v>
+        <v>1.6676</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.0844</v>
+        <v>-0.0833</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.2773</v>
+        <v>0.3121</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.8071</v>
+        <v>-0.3955</v>
       </c>
       <c r="V11" t="n">
-        <v>-2.6436</v>
+        <v>-1.2589</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>0.3144</v>
       </c>
       <c r="X11" t="n">
-        <v>-2.6436</v>
+        <v>-1.5733</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-8.090199999999999</v>
+        <v>-6.2842</v>
       </c>
       <c r="E12" t="n">
-        <v>-4.8759</v>
+        <v>-3.3408</v>
       </c>
       <c r="F12" t="n">
-        <v>-3.2143</v>
+        <v>-2.9434</v>
       </c>
       <c r="G12" t="n">
         <v>-1.8428</v>
@@ -1390,13 +1390,13 @@
         <v>2.9646</v>
       </c>
       <c r="S12" t="n">
-        <v>-2.2157</v>
+        <v>-0.4098</v>
       </c>
       <c r="T12" t="n">
-        <v>-1.3679</v>
+        <v>0.1673</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.8479</v>
+        <v>-0.577</v>
       </c>
       <c r="V12" t="n">
         <v>-4.2169</v>
@@ -1423,22 +1423,22 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>11.7656</v>
+        <v>12.5865</v>
       </c>
       <c r="E13" t="n">
-        <v>11.7916</v>
+        <v>12.6121</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.02590000000000048</v>
+        <v>-0.02579999999999982</v>
       </c>
       <c r="G13" t="n">
-        <v>8.515200000000002</v>
+        <v>8.5152</v>
       </c>
       <c r="H13" t="n">
-        <v>8.400000000000002</v>
+        <v>8.4</v>
       </c>
       <c r="I13" t="n">
-        <v>0.1150999999999998</v>
+        <v>0.1151</v>
       </c>
       <c r="J13" t="n">
         <v>12.2811</v>
@@ -1459,7 +1459,7 @@
         <v>0.7308999999999998</v>
       </c>
       <c r="P13" t="n">
-        <v>3.7057</v>
+        <v>3.705699999999999</v>
       </c>
       <c r="Q13" t="n">
         <v>-12.0435</v>
@@ -1468,19 +1468,19 @@
         <v>15.7494</v>
       </c>
       <c r="S13" t="n">
-        <v>1.747200000000001</v>
+        <v>2.567799999999999</v>
       </c>
       <c r="T13" t="n">
-        <v>3.0593</v>
+        <v>3.88</v>
       </c>
       <c r="U13" t="n">
-        <v>-1.3121</v>
+        <v>-1.312</v>
       </c>
       <c r="V13" t="n">
-        <v>-2.202099999999999</v>
+        <v>-2.2021</v>
       </c>
       <c r="W13" t="n">
-        <v>8.494799999999998</v>
+        <v>8.494800000000001</v>
       </c>
       <c r="X13" t="n">
         <v>-10.6969</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>J. SANCHEZ BARQUIN</t>
+          <t>M. CASERO MIGLIAVACCA</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,64 +1501,64 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>2.651</v>
+        <v>3.3677</v>
       </c>
       <c r="E14" t="n">
-        <v>3.7291</v>
+        <v>3.5693</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.078</v>
+        <v>-0.2016</v>
       </c>
       <c r="G14" t="n">
-        <v>0.2288</v>
+        <v>2.7266</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.4671</v>
+        <v>0.8374</v>
       </c>
       <c r="I14" t="n">
-        <v>0.696</v>
+        <v>1.8892</v>
       </c>
       <c r="J14" t="n">
-        <v>2.2822</v>
+        <v>4.5101</v>
       </c>
       <c r="K14" t="n">
-        <v>1.4943</v>
+        <v>3.1818</v>
       </c>
       <c r="L14" t="n">
-        <v>0.788</v>
+        <v>1.3283</v>
       </c>
       <c r="M14" t="n">
-        <v>-2.0534</v>
+        <v>-1.7835</v>
       </c>
       <c r="N14" t="n">
-        <v>-1.9614</v>
+        <v>-2.3444</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.092</v>
+        <v>0.5609</v>
       </c>
       <c r="P14" t="n">
         <v>1.8529</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>-0.1853</v>
       </c>
       <c r="R14" t="n">
-        <v>1.8529</v>
+        <v>2.0382</v>
       </c>
       <c r="S14" t="n">
-        <v>-1.0045</v>
+        <v>-0.2674</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.4414</v>
+        <v>-0.1256</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.5631</v>
+        <v>-0.1418</v>
       </c>
       <c r="V14" t="n">
-        <v>1.5738</v>
+        <v>-0.9444</v>
       </c>
       <c r="W14" t="n">
-        <v>1.8883</v>
+        <v>-0.63</v>
       </c>
       <c r="X14" t="n">
         <v>-0.3144</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>M. CASERO MIGLIAVACCA</t>
+          <t>J. SANCHEZ BARQUIN</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,64 +1579,64 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.4365</v>
+        <v>2.9946</v>
       </c>
       <c r="E15" t="n">
-        <v>2.7858</v>
+        <v>3.9249</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.3493</v>
+        <v>-0.9303</v>
       </c>
       <c r="G15" t="n">
-        <v>2.7266</v>
+        <v>0.2288</v>
       </c>
       <c r="H15" t="n">
-        <v>0.8374</v>
+        <v>-0.4671</v>
       </c>
       <c r="I15" t="n">
-        <v>1.8892</v>
+        <v>0.696</v>
       </c>
       <c r="J15" t="n">
-        <v>4.5101</v>
+        <v>2.2822</v>
       </c>
       <c r="K15" t="n">
-        <v>3.1818</v>
+        <v>1.4943</v>
       </c>
       <c r="L15" t="n">
-        <v>1.3283</v>
+        <v>0.788</v>
       </c>
       <c r="M15" t="n">
-        <v>-1.7835</v>
+        <v>-2.0534</v>
       </c>
       <c r="N15" t="n">
-        <v>-2.3444</v>
+        <v>-1.9614</v>
       </c>
       <c r="O15" t="n">
-        <v>0.5609</v>
+        <v>-0.092</v>
       </c>
       <c r="P15" t="n">
         <v>1.8529</v>
       </c>
       <c r="Q15" t="n">
-        <v>-0.1853</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>2.0382</v>
+        <v>1.8529</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.1985</v>
+        <v>-0.6609</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.909</v>
+        <v>-0.2456</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.2895</v>
+        <v>-0.4154</v>
       </c>
       <c r="V15" t="n">
-        <v>-0.9444</v>
+        <v>1.5738</v>
       </c>
       <c r="W15" t="n">
-        <v>-0.63</v>
+        <v>1.8883</v>
       </c>
       <c r="X15" t="n">
         <v>-0.3144</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>S. KALLE</t>
+          <t>B. LEON TEJERA</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.2533</v>
+        <v>1.6735</v>
       </c>
       <c r="E16" t="n">
-        <v>1.8519</v>
+        <v>3.4818</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.5986</v>
+        <v>-1.8083</v>
       </c>
       <c r="G16" t="n">
-        <v>1.0778</v>
+        <v>-0.1466</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.2095</v>
+        <v>-0.4033</v>
       </c>
       <c r="I16" t="n">
-        <v>1.2872</v>
+        <v>0.2566</v>
       </c>
       <c r="J16" t="n">
-        <v>1.6723</v>
+        <v>0.2562</v>
       </c>
       <c r="K16" t="n">
-        <v>0.8844</v>
+        <v>0.2147</v>
       </c>
       <c r="L16" t="n">
-        <v>0.788</v>
+        <v>0.0415</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.5945</v>
+        <v>-0.4028</v>
       </c>
       <c r="N16" t="n">
-        <v>-1.0938</v>
+        <v>-0.618</v>
       </c>
       <c r="O16" t="n">
-        <v>0.4993</v>
+        <v>0.2152</v>
       </c>
       <c r="P16" t="n">
-        <v>0.1853</v>
+        <v>-0.5558999999999999</v>
       </c>
       <c r="Q16" t="n">
-        <v>-0.9264</v>
+        <v>-1.1117</v>
       </c>
       <c r="R16" t="n">
-        <v>1.1117</v>
+        <v>0.5558999999999999</v>
       </c>
       <c r="S16" t="n">
-        <v>1.878</v>
+        <v>-0.1411</v>
       </c>
       <c r="T16" t="n">
-        <v>1.736</v>
+        <v>0.2469</v>
       </c>
       <c r="U16" t="n">
-        <v>0.142</v>
+        <v>-0.388</v>
       </c>
       <c r="V16" t="n">
-        <v>-1.8877</v>
+        <v>2.5172</v>
       </c>
       <c r="W16" t="n">
-        <v>-0.63</v>
+        <v>4.0904</v>
       </c>
       <c r="X16" t="n">
-        <v>-1.2578</v>
+        <v>-1.5733</v>
       </c>
     </row>
     <row r="17">
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>B. LEON TEJERA</t>
+          <t>A. PARRA RIVERA</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.889</v>
+        <v>0.1614</v>
       </c>
       <c r="E18" t="n">
-        <v>2.8942</v>
+        <v>0.3757</v>
       </c>
       <c r="F18" t="n">
-        <v>-2.0052</v>
+        <v>-0.2143</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.1466</v>
+        <v>-1.491</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.4033</v>
+        <v>-1.528</v>
       </c>
       <c r="I18" t="n">
-        <v>0.2566</v>
+        <v>0.0369</v>
       </c>
       <c r="J18" t="n">
-        <v>0.2562</v>
+        <v>-0.7719</v>
       </c>
       <c r="K18" t="n">
-        <v>0.2147</v>
+        <v>-0.8548</v>
       </c>
       <c r="L18" t="n">
-        <v>0.0415</v>
+        <v>0.0829</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.4028</v>
+        <v>-0.7191</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.618</v>
+        <v>-0.6731</v>
       </c>
       <c r="O18" t="n">
-        <v>0.2152</v>
+        <v>-0.046</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.5558999999999999</v>
+        <v>0.1853</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.1117</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>0.5558999999999999</v>
+        <v>0.1853</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.9257</v>
+        <v>0.2083</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.3407</v>
+        <v>-0.1113</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.585</v>
+        <v>0.3196</v>
       </c>
       <c r="V18" t="n">
-        <v>2.5172</v>
+        <v>1.2589</v>
       </c>
       <c r="W18" t="n">
-        <v>4.0904</v>
+        <v>1.2589</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.5733</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A. PARRA RIVERA</t>
+          <t>S. KALLE</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.0641</v>
+        <v>-0.1434</v>
       </c>
       <c r="E19" t="n">
-        <v>0.1798</v>
+        <v>0.6768</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.1158</v>
+        <v>-0.8202</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.491</v>
+        <v>1.0778</v>
       </c>
       <c r="H19" t="n">
-        <v>-1.528</v>
+        <v>-0.2095</v>
       </c>
       <c r="I19" t="n">
-        <v>0.0369</v>
+        <v>1.2872</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.7719</v>
+        <v>1.6723</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.8548</v>
+        <v>0.8844</v>
       </c>
       <c r="L19" t="n">
-        <v>0.0829</v>
+        <v>0.788</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.7191</v>
+        <v>-0.5945</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.6731</v>
+        <v>-1.0938</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.046</v>
+        <v>0.4993</v>
       </c>
       <c r="P19" t="n">
         <v>0.1853</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>-0.9264</v>
       </c>
       <c r="R19" t="n">
-        <v>0.1853</v>
+        <v>1.1117</v>
       </c>
       <c r="S19" t="n">
-        <v>0.1109</v>
+        <v>0.4813</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.3071</v>
+        <v>0.5609</v>
       </c>
       <c r="U19" t="n">
-        <v>0.4181</v>
+        <v>-0.0796</v>
       </c>
       <c r="V19" t="n">
-        <v>1.2589</v>
+        <v>-1.8877</v>
       </c>
       <c r="W19" t="n">
-        <v>1.2589</v>
+        <v>-0.63</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>-1.2578</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.017</v>
+        <v>-1.7468</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.8524</v>
+        <v>-1.7545</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.1647</v>
+        <v>0.0077</v>
       </c>
       <c r="G20" t="n">
         <v>-0.5949</v>
@@ -2014,13 +2014,13 @@
         <v>0.1853</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.681</v>
+        <v>-0.4107</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.383</v>
+        <v>-0.2851</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.298</v>
+        <v>-0.1256</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.1576</v>
+        <v>-3.8448</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.3386</v>
+        <v>-1.7303</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.819</v>
+        <v>-2.1145</v>
       </c>
       <c r="G21" t="n">
         <v>-5.3124</v>
@@ -2092,13 +2092,13 @@
         <v>2.2234</v>
       </c>
       <c r="S21" t="n">
-        <v>0.4136</v>
+        <v>-0.2736</v>
       </c>
       <c r="T21" t="n">
-        <v>0.8307</v>
+        <v>0.439</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.4171</v>
+        <v>-0.7126</v>
       </c>
       <c r="V21" t="n">
         <v>0.6294</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-4.4035</v>
+        <v>-4.8192</v>
       </c>
       <c r="E22" t="n">
-        <v>-3.0003</v>
+        <v>-3.49</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.4031</v>
+        <v>-1.3293</v>
       </c>
       <c r="G22" t="n">
         <v>-2.31</v>
@@ -2170,13 +2170,13 @@
         <v>1.297</v>
       </c>
       <c r="S22" t="n">
-        <v>0.2221</v>
+        <v>-0.1937</v>
       </c>
       <c r="T22" t="n">
-        <v>0.7461</v>
+        <v>0.2565</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.524</v>
+        <v>-0.4502</v>
       </c>
       <c r="V22" t="n">
         <v>-1.5744</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-4.4328</v>
+        <v>-5.0467</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.6761</v>
+        <v>-3.9699</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.7568</v>
+        <v>-1.0769</v>
       </c>
       <c r="G23" t="n">
         <v>-1.3767</v>
@@ -2248,13 +2248,13 @@
         <v>0.7411</v>
       </c>
       <c r="S23" t="n">
-        <v>1.0202</v>
+        <v>0.4063</v>
       </c>
       <c r="T23" t="n">
-        <v>0.9103</v>
+        <v>0.6165</v>
       </c>
       <c r="U23" t="n">
-        <v>0.1099</v>
+        <v>-0.2102</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-5.9928</v>
+        <v>-5.3061</v>
       </c>
       <c r="E24" t="n">
-        <v>-2.4918</v>
+        <v>-2.0022</v>
       </c>
       <c r="F24" t="n">
-        <v>-3.5009</v>
+        <v>-3.3039</v>
       </c>
       <c r="G24" t="n">
         <v>-2.2606</v>
@@ -2326,13 +2326,13 @@
         <v>1.8529</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.5823</v>
+        <v>-0.8957000000000001</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.5296999999999999</v>
+        <v>-0.0401</v>
       </c>
       <c r="U24" t="n">
-        <v>-1.0525</v>
+        <v>-0.8556</v>
       </c>
       <c r="V24" t="n">
         <v>0.6294</v>
@@ -2362,28 +2362,28 @@
         <v>-11.7657</v>
       </c>
       <c r="E25" t="n">
-        <v>0.02570000000000094</v>
+        <v>0.02569999999999961</v>
       </c>
       <c r="F25" t="n">
-        <v>-11.7914</v>
+        <v>-11.7916</v>
       </c>
       <c r="G25" t="n">
-        <v>-8.514900000000001</v>
+        <v>-8.514899999999999</v>
       </c>
       <c r="H25" t="n">
         <v>-8.399999999999999</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.1150999999999999</v>
+        <v>-0.1151000000000005</v>
       </c>
       <c r="J25" t="n">
-        <v>3.766100000000002</v>
+        <v>3.766100000000001</v>
       </c>
       <c r="K25" t="n">
-        <v>4.497000000000002</v>
+        <v>4.497000000000001</v>
       </c>
       <c r="L25" t="n">
-        <v>-0.7308</v>
+        <v>-0.7308000000000004</v>
       </c>
       <c r="M25" t="n">
         <v>-12.281</v>
@@ -2407,13 +2407,13 @@
         <v>-1.7472</v>
       </c>
       <c r="T25" t="n">
-        <v>1.3122</v>
+        <v>1.3121</v>
       </c>
       <c r="U25" t="n">
-        <v>-3.0592</v>
+        <v>-3.0594</v>
       </c>
       <c r="V25" t="n">
-        <v>2.2022</v>
+        <v>2.202199999999999</v>
       </c>
       <c r="W25" t="n">
         <v>10.6968</v>
